--- a/artfynd/A 37346-2021 artfynd.xlsx
+++ b/artfynd/A 37346-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37346-2021 artfynd.xlsx
+++ b/artfynd/A 37346-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74469323</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563820.0159985332</v>
+        <v>563820</v>
       </c>
       <c r="R2" t="n">
-        <v>6371803.106173382</v>
+        <v>6371803</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 37346-2021 artfynd.xlsx
+++ b/artfynd/A 37346-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469323</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37346-2021 artfynd.xlsx
+++ b/artfynd/A 37346-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469323</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37346-2021 artfynd.xlsx
+++ b/artfynd/A 37346-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469323</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37346-2021 artfynd.xlsx
+++ b/artfynd/A 37346-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469323</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37346-2021 artfynd.xlsx
+++ b/artfynd/A 37346-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469323</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37346-2021 artfynd.xlsx
+++ b/artfynd/A 37346-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469323</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37346-2021 artfynd.xlsx
+++ b/artfynd/A 37346-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469323</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37346-2021 artfynd.xlsx
+++ b/artfynd/A 37346-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469323</v>
       </c>
       <c r="B2" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37346-2021 artfynd.xlsx
+++ b/artfynd/A 37346-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469323</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37346-2021 artfynd.xlsx
+++ b/artfynd/A 37346-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74469323</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37346-2021 artfynd.xlsx
+++ b/artfynd/A 37346-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>74469323</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,6 +783,240 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114710055</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Häll 1:2, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>563665</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6371995</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vena</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-02-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>80-årig barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Inge Jonsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Inge Jonsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126912199</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Häll 1:2,, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563674</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6371987</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vena</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inge Jonsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inge Jonsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
